--- a/outputs/56419.xlsx
+++ b/outputs/56419.xlsx
@@ -212,20 +212,24 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -482,1184 +486,1184 @@
   <dimension ref="A1:H100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.82"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <f aca="false">IF(B2&lt;&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <f aca="false">SUM($D$2:D2)</f>
         <v>1</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="1" t="n">
+      <c r="F2" s="3"/>
+      <c r="G2" s="2" t="n">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>2</v>
       </c>
-      <c r="H2" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H2" s="4" t="str">
+        <f aca="false" t="array" ref="H2:H2">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H2))),"")</f>
         <v>A</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <f aca="false">IF(B3&lt;&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <f aca="false">SUM($D$2:D3)</f>
         <v>2</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="1" t="n">
+      <c r="F3" s="3"/>
+      <c r="G3" s="2" t="n">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>3</v>
       </c>
-      <c r="H3" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H3" s="4" t="str">
+        <f aca="false" t="array" ref="H3:H3">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H3))),"")</f>
         <v>B</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="n">
+      <c r="B4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <f aca="false">IF(B4&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <f aca="false">SUM($D$2:D4)</f>
         <v>2</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="1" t="n">
+      <c r="F4" s="3"/>
+      <c r="G4" s="2" t="n">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>5</v>
       </c>
-      <c r="H4" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H4" s="4" t="str">
+        <f aca="false" t="array" ref="H4:H4">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H4))),"")</f>
         <v>D</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <f aca="false">IF(B5&lt;&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <f aca="false">SUM($D$2:D5)</f>
         <v>3</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="1" t="n">
+      <c r="F5" s="3"/>
+      <c r="G5" s="2" t="n">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>6</v>
       </c>
-      <c r="H5" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H5" s="4" t="str">
+        <f aca="false" t="array" ref="H5:H5">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H5))),"")</f>
         <v>E</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <f aca="false">IF(B6&lt;&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <f aca="false">SUM($D$2:D6)</f>
         <v>4</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="1" t="n">
+      <c r="F6" s="3"/>
+      <c r="G6" s="2" t="n">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>9</v>
       </c>
-      <c r="H6" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H6" s="4" t="str">
+        <f aca="false" t="array" ref="H6:H6">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H6))),"")</f>
         <v>H</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="n">
+      <c r="B7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <f aca="false">IF(B7&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <f aca="false">SUM($D$2:D7)</f>
         <v>4</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="1" t="n">
+      <c r="F7" s="3"/>
+      <c r="G7" s="2" t="n">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>10</v>
       </c>
-      <c r="H7" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H7" s="4" t="str">
+        <f aca="false" t="array" ref="H7:H7">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H7))),"")</f>
         <v>I</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="B8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <f aca="false">IF(B8&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="3" t="n">
         <f aca="false">SUM($D$2:D8)</f>
         <v>4</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="1" t="n">
+      <c r="F8" s="3"/>
+      <c r="G8" s="2" t="n">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>13</v>
       </c>
-      <c r="H8" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H8" s="4" t="str">
+        <f aca="false" t="array" ref="H8:H8">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H8))),"")</f>
         <v>L</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <f aca="false">IF(B9&lt;&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <f aca="false">SUM($D$2:D9)</f>
         <v>5</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="1" t="n">
+      <c r="F9" s="3"/>
+      <c r="G9" s="2" t="n">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>15</v>
       </c>
-      <c r="H9" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H9" s="4" t="str">
+        <f aca="false" t="array" ref="H9:H9">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H9))),"")</f>
         <v>N</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>2.4</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <f aca="false">IF(B10&lt;&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="3" t="n">
         <f aca="false">SUM($D$2:D10)</f>
         <v>6</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="1" t="n">
+      <c r="F10" s="3"/>
+      <c r="G10" s="2" t="n">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>21</v>
       </c>
-      <c r="H10" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H10" s="4" t="str">
+        <f aca="false" t="array" ref="H10:H10">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H10))),"")</f>
         <v>T</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2" t="n">
+      <c r="B11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
         <f aca="false">IF(B11&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="3" t="n">
         <f aca="false">SUM($D$2:D11)</f>
         <v>6</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="1" t="n">
+      <c r="F11" s="3"/>
+      <c r="G11" s="2" t="n">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>25</v>
       </c>
-      <c r="H11" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H11" s="4" t="str">
+        <f aca="false" t="array" ref="H11:H11">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H11))),"")</f>
         <v>X</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2" t="n">
+      <c r="B12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
         <f aca="false">IF(B12&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="3" t="n">
         <f aca="false">SUM($D$2:D12)</f>
         <v>6</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="1" t="e">
+      <c r="F12" s="3"/>
+      <c r="G12" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H12" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H12" s="4" t="str">
+        <f aca="false" t="array" ref="H12:H12">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H12))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="3" t="n">
         <f aca="false">IF(B13&lt;&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="3" t="n">
         <f aca="false">SUM($D$2:D13)</f>
         <v>7</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="1" t="e">
+      <c r="F13" s="3"/>
+      <c r="G13" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H13" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H13" s="4" t="str">
+        <f aca="false" t="array" ref="H13:H13">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H13))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2" t="n">
+      <c r="B14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
         <f aca="false">IF(B14&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="3" t="n">
         <f aca="false">SUM($D$2:D14)</f>
         <v>7</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="1" t="e">
+      <c r="F14" s="3"/>
+      <c r="G14" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H14" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H14" s="4" t="str">
+        <f aca="false" t="array" ref="H14:H14">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H14))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="3" t="n">
         <f aca="false">IF(B15&lt;&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="3" t="n">
         <f aca="false">SUM($D$2:D15)</f>
         <v>8</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="1" t="e">
+      <c r="F15" s="3"/>
+      <c r="G15" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H15" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H15" s="4" t="str">
+        <f aca="false" t="array" ref="H15:H15">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H15))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2" t="n">
+      <c r="B16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <f aca="false">IF(B16&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="3" t="n">
         <f aca="false">SUM($D$2:D16)</f>
         <v>8</v>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="1" t="e">
+      <c r="F16" s="3"/>
+      <c r="G16" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H16" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H16" s="4" t="str">
+        <f aca="false" t="array" ref="H16:H16">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H16))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2" t="n">
+      <c r="B17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
         <f aca="false">IF(B17&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="3" t="n">
         <f aca="false">SUM($D$2:D17)</f>
         <v>8</v>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="1" t="e">
+      <c r="F17" s="3"/>
+      <c r="G17" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H17" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H17" s="4" t="str">
+        <f aca="false" t="array" ref="H17:H17">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H17))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="2" t="n">
+      <c r="B18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <f aca="false">IF(B18&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="3" t="n">
         <f aca="false">SUM($D$2:D18)</f>
         <v>8</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="1" t="e">
+      <c r="F18" s="3"/>
+      <c r="G18" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H18" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H18" s="4" t="str">
+        <f aca="false" t="array" ref="H18:H18">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H18))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="2" t="n">
+      <c r="B19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
         <f aca="false">IF(B19&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="3" t="n">
         <f aca="false">SUM($D$2:D19)</f>
         <v>8</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="1" t="e">
+      <c r="F19" s="3"/>
+      <c r="G19" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H19" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H19" s="4" t="str">
+        <f aca="false" t="array" ref="H19:H19">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H19))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="2" t="n">
+      <c r="B20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
         <f aca="false">IF(B20&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="3" t="n">
         <f aca="false">SUM($D$2:D20)</f>
         <v>8</v>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="1" t="e">
+      <c r="F20" s="3"/>
+      <c r="G20" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H20" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H20" s="4" t="str">
+        <f aca="false" t="array" ref="H20:H20">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H20))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="3" t="n">
         <f aca="false">IF(B21&lt;&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="3" t="n">
         <f aca="false">SUM($D$2:D21)</f>
         <v>9</v>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="1" t="e">
+      <c r="F21" s="3"/>
+      <c r="G21" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H21" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H21" s="4" t="str">
+        <f aca="false" t="array" ref="H21:H21">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H21))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="2" t="n">
+      <c r="B22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <f aca="false">IF(B22&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="3" t="n">
         <f aca="false">SUM($D$2:D22)</f>
         <v>9</v>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="1" t="e">
+      <c r="F22" s="3"/>
+      <c r="G22" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H22" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H22" s="4" t="str">
+        <f aca="false" t="array" ref="H22:H22">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H22))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="2" t="n">
+      <c r="B23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n">
         <f aca="false">IF(B23&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="3" t="n">
         <f aca="false">SUM($D$2:D23)</f>
         <v>9</v>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="1" t="e">
+      <c r="F23" s="3"/>
+      <c r="G23" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H23" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H23" s="4" t="str">
+        <f aca="false" t="array" ref="H23:H23">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H23))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="2" t="n">
+      <c r="B24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
         <f aca="false">IF(B24&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="3" t="n">
         <f aca="false">SUM($D$2:D24)</f>
         <v>9</v>
       </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="1" t="e">
+      <c r="F24" s="3"/>
+      <c r="G24" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H24" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H24" s="4" t="str">
+        <f aca="false" t="array" ref="H24:H24">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H24))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="3" t="n">
         <f aca="false">IF(B25&lt;&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="3" t="n">
         <f aca="false">SUM($D$2:D25)</f>
         <v>10</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="1" t="e">
+      <c r="F25" s="3"/>
+      <c r="G25" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H25" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H25" s="4" t="str">
+        <f aca="false" t="array" ref="H25:H25">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H25))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2" t="n">
+      <c r="B26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
         <f aca="false">IF(B26&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="3" t="n">
         <f aca="false">SUM($D$2:D26)</f>
         <v>10</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="1" t="e">
+      <c r="F26" s="3"/>
+      <c r="G26" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H26" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H26" s="4" t="str">
+        <f aca="false" t="array" ref="H26:H26">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H26))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="2" t="n">
+      <c r="B27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="n">
         <f aca="false">IF(B27&lt;&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="3" t="n">
         <f aca="false">SUM($D$2:D27)</f>
         <v>10</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="1" t="e">
+      <c r="F27" s="3"/>
+      <c r="G27" s="2" t="e">
         <f aca="false">MATCH(ROW()-ROW($B$1),$E:$E,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H27" s="3" t="str">
-        <f aca="false">IFERROR(INDEX($A$2:$A$27,MATCH(ROW()-ROW($B$1),MMULT(--(ROW($B$2:$B$27)&gt;=TRANSPOSE(ROW($B$2:$B$27))),--($B$2:$B$27&lt;&gt;0)),0)),"")</f>
+      <c r="H27" s="4" t="str">
+        <f aca="false" t="array" ref="H27:H27">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H27))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-    </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-    </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-    </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-    </row>
-    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-    </row>
-    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-    </row>
-    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-    </row>
-    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-    </row>
-    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-    </row>
-    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-    </row>
-    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-    </row>
-    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-    </row>
-    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-    </row>
-    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-    </row>
-    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-    </row>
-    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-    </row>
-    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-    </row>
-    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-    </row>
-    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-    </row>
-    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-    </row>
-    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-    </row>
-    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-    </row>
-    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-    </row>
-    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-    </row>
-    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-    </row>
-    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-    </row>
-    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-    </row>
-    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-    </row>
-    <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-    </row>
-    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-    </row>
-    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-    </row>
-    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-    </row>
-    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-    </row>
-    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-    </row>
-    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-    </row>
-    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-    </row>
-    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-    </row>
-    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-    </row>
-    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-    </row>
-    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-    </row>
-    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-    </row>
-    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-    </row>
-    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-    </row>
-    <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-    </row>
-    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-    </row>
-    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-    </row>
-    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-    </row>
-    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
-    </row>
-    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-    </row>
-    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-    </row>
-    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-    </row>
-    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1"/>
-    </row>
-    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-    </row>
-    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-    </row>
-    <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-    </row>
-    <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
-    </row>
-    <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="1"/>
-      <c r="H94" s="1"/>
-    </row>
-    <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
-    </row>
-    <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="1"/>
-      <c r="H96" s="1"/>
-    </row>
-    <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="1"/>
-      <c r="H97" s="1"/>
-    </row>
-    <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="1"/>
-      <c r="H98" s="1"/>
-    </row>
-    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
-    </row>
-    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1"/>
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+    </row>
+    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+    </row>
+    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+    </row>
+    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+    </row>
+    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+    </row>
+    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+    </row>
+    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+    </row>
+    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+    </row>
+    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+    </row>
+    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+    </row>
+    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+    </row>
+    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+    </row>
+    <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+    </row>
+    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+    </row>
+    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+    </row>
+    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+    </row>
+    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+    </row>
+    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+    </row>
+    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+    </row>
+    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+    </row>
+    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+    </row>
+    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+    </row>
+    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+    </row>
+    <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+    </row>
+    <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+    </row>
+    <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+    </row>
+    <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+    </row>
+    <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+    </row>
+    <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+    </row>
+    <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+    </row>
+    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+    </row>
+    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/56419.xlsx
+++ b/outputs/56419.xlsx
@@ -221,7 +221,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -229,7 +229,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -489,7 +489,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.82"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -504,7 +504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -525,11 +525,11 @@
         <v>2</v>
       </c>
       <c r="H2" s="4" t="str">
-        <f aca="false" t="array" ref="H2:H2">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H2))),"")</f>
+        <f aca="false">IF(B2&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
         <v>A</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -550,11 +550,11 @@
         <v>3</v>
       </c>
       <c r="H3" s="4" t="str">
-        <f aca="false" t="array" ref="H3:H3">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H3))),"")</f>
+        <f aca="false">IF(B3&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
         <v>B</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -575,11 +575,11 @@
         <v>5</v>
       </c>
       <c r="H4" s="4" t="str">
-        <f aca="false" t="array" ref="H4:H4">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H4))),"")</f>
-        <v>D</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(B4&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -600,11 +600,11 @@
         <v>6</v>
       </c>
       <c r="H5" s="4" t="str">
-        <f aca="false" t="array" ref="H5:H5">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H5))),"")</f>
-        <v>E</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(B5&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
+        <v>D</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -625,11 +625,11 @@
         <v>9</v>
       </c>
       <c r="H6" s="4" t="str">
-        <f aca="false" t="array" ref="H6:H6">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H6))),"")</f>
-        <v>H</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(B6&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
+        <v>E</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -650,11 +650,11 @@
         <v>10</v>
       </c>
       <c r="H7" s="4" t="str">
-        <f aca="false" t="array" ref="H7:H7">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H7))),"")</f>
-        <v>I</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(B7&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -675,11 +675,11 @@
         <v>13</v>
       </c>
       <c r="H8" s="4" t="str">
-        <f aca="false" t="array" ref="H8:H8">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H8))),"")</f>
-        <v>L</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(B8&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -700,11 +700,11 @@
         <v>15</v>
       </c>
       <c r="H9" s="4" t="str">
-        <f aca="false" t="array" ref="H9:H9">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H9))),"")</f>
-        <v>N</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(B9&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
+        <v>H</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -725,11 +725,11 @@
         <v>21</v>
       </c>
       <c r="H10" s="4" t="str">
-        <f aca="false" t="array" ref="H10:H10">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H10))),"")</f>
-        <v>T</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(B10&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
+        <v>I</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -750,11 +750,11 @@
         <v>25</v>
       </c>
       <c r="H11" s="4" t="str">
-        <f aca="false" t="array" ref="H11:H11">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H11))),"")</f>
-        <v>X</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(B11&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -775,11 +775,11 @@
         <v>#N/A</v>
       </c>
       <c r="H12" s="4" t="str">
-        <f aca="false" t="array" ref="H12:H12">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H12))),"")</f>
+        <f aca="false">IF(B12&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -800,11 +800,11 @@
         <v>#N/A</v>
       </c>
       <c r="H13" s="4" t="str">
-        <f aca="false" t="array" ref="H13:H13">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H13))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(B13&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
+        <v>L</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -825,11 +825,11 @@
         <v>#N/A</v>
       </c>
       <c r="H14" s="4" t="str">
-        <f aca="false" t="array" ref="H14:H14">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H14))),"")</f>
+        <f aca="false">IF(B14&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -850,11 +850,11 @@
         <v>#N/A</v>
       </c>
       <c r="H15" s="4" t="str">
-        <f aca="false" t="array" ref="H15:H15">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H15))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(B15&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -875,11 +875,11 @@
         <v>#N/A</v>
       </c>
       <c r="H16" s="4" t="str">
-        <f aca="false" t="array" ref="H16:H16">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H16))),"")</f>
+        <f aca="false">IF(B16&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -900,11 +900,11 @@
         <v>#N/A</v>
       </c>
       <c r="H17" s="4" t="str">
-        <f aca="false" t="array" ref="H17:H17">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H17))),"")</f>
+        <f aca="false">IF(B17&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -925,11 +925,11 @@
         <v>#N/A</v>
       </c>
       <c r="H18" s="4" t="str">
-        <f aca="false" t="array" ref="H18:H18">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H18))),"")</f>
+        <f aca="false">IF(B18&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -950,11 +950,11 @@
         <v>#N/A</v>
       </c>
       <c r="H19" s="4" t="str">
-        <f aca="false" t="array" ref="H19:H19">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H19))),"")</f>
+        <f aca="false">IF(B19&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -975,11 +975,11 @@
         <v>#N/A</v>
       </c>
       <c r="H20" s="4" t="str">
-        <f aca="false" t="array" ref="H20:H20">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H20))),"")</f>
+        <f aca="false">IF(B20&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
@@ -1000,11 +1000,11 @@
         <v>#N/A</v>
       </c>
       <c r="H21" s="4" t="str">
-        <f aca="false" t="array" ref="H21:H21">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H21))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(B21&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
+        <v>T</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -1025,11 +1025,11 @@
         <v>#N/A</v>
       </c>
       <c r="H22" s="4" t="str">
-        <f aca="false" t="array" ref="H22:H22">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H22))),"")</f>
+        <f aca="false">IF(B22&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -1050,11 +1050,11 @@
         <v>#N/A</v>
       </c>
       <c r="H23" s="4" t="str">
-        <f aca="false" t="array" ref="H23:H23">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H23))),"")</f>
+        <f aca="false">IF(B23&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -1075,11 +1075,11 @@
         <v>#N/A</v>
       </c>
       <c r="H24" s="4" t="str">
-        <f aca="false" t="array" ref="H24:H24">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H24))),"")</f>
+        <f aca="false">IF(B24&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -1100,11 +1100,11 @@
         <v>#N/A</v>
       </c>
       <c r="H25" s="4" t="str">
-        <f aca="false" t="array" ref="H25:H25">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H25))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(B25&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
+        <v>X</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -1125,11 +1125,11 @@
         <v>#N/A</v>
       </c>
       <c r="H26" s="4" t="str">
-        <f aca="false" t="array" ref="H26:H26">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H26))),"")</f>
+        <f aca="false">IF(B26&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -1150,515 +1150,515 @@
         <v>#N/A</v>
       </c>
       <c r="H27" s="4" t="str">
-        <f aca="false" t="array" ref="H27:H27">IFERROR(INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-1),ROWS($H$2:H27))),"")</f>
+        <f aca="false">IF(B27&lt;&gt;0,INDEX($A$2:$A$27,SMALL(IF($B$2:$B$27&lt;&gt;0,ROW($B$2:$B$27)-ROW($B$1)),ROW()-ROW($B$1))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
     </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
     </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
     </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
     </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
     </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
     </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
     </row>
-    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
     </row>
-    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
     </row>
-    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
     </row>
-    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
     </row>
-    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
     </row>
-    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
     </row>
-    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
     </row>
-    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
     </row>
-    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
     </row>
-    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
     </row>
-    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
     </row>
-    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
     </row>
-    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
     </row>
-    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
     </row>
-    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
     </row>
-    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
     </row>
-    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
     </row>
-    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
     </row>
-    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
     </row>
-    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
     </row>
-    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
     </row>
-    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
     </row>
-    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
     </row>
-    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
     </row>
-    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
     </row>
-    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
     </row>
-    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
     </row>
-    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
     </row>
-    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
     </row>
-    <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
     </row>
-    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
     </row>
-    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
     </row>
-    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
     </row>
-    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
     </row>
-    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
     </row>
-    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
     </row>
-    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
     </row>
-    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
     </row>
-    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
     </row>
-    <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
     </row>
-    <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
     </row>
-    <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
     </row>
-    <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
     </row>
-    <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
     </row>
-    <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
     </row>
-    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
     </row>
-    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
